--- a/knowledge_base/erc_solar_physics_expenses.xlsx
+++ b/knowledge_base/erc_solar_physics_expenses.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERC_Grant_Expenses" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
-  </numFmts>
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,32 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F4F4F"/>
-        <bgColor rgb="002F4F4F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-        <bgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,47 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D3D3D3"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D3D3D3"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D3D3D3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D3D3D3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,577 +413,673 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Transaction_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Amount_EUR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERC_Budget_Line</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Compliance_Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TRX-2026-101</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Personnel</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Postdoc Stipend (Q1) - Dr. A. Novak</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" t="n">
         <v>12500</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>A.1. Staff</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TRX-2026-102</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2026-01-22</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>AWS EC2 Instance (A100 GPUs) for pKAN training</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" t="n">
         <v>4250.75</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>B.2. Consumables</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TRX-2026-103</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Flights &amp; Accommodation - European Geosciences Union (Vienna)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" t="n">
         <v>1150</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>B.1. Travel</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Pending Audit</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TRX-2026-104</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>4x 16TB NAS Drives for Solar Orbiter telemetry storage</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" t="n">
         <v>1840.5</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>B.3. Equipment</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TRX-2026-105</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Publications</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Open Access Fee - Astronomy &amp; Astrophysics Journal</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" t="n">
         <v>2200</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>B.4. Publications</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TRX-2026-106</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>HPC Cluster allocation - Magnetic field topology simulations</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" t="n">
         <v>3800</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>B.2. Consumables</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TRX-2026-107</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Personnel</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Undergraduate Summer Research Intern (UROP) - SciML focus</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" t="n">
         <v>3500</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>A.1. Staff</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TRX-2026-108</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Registration Fee - Solar Physics Summit</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" t="n">
         <v>450</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>B.1. Travel</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TRX-2026-109</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>High-performance workstation components (RAM upgrade)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" t="n">
         <v>680.2</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>B.2. Consumables</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Requires PI Justification</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>TRX-2026-110</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Cloud Compute - Symbolic regression pipelines</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" t="n">
         <v>2150.9</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>B.2. Consumables</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>TRX-2026-111</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Train travel to collaborative workshop at KU Leuven</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" t="n">
         <v>280</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>B.1. Travel</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>TRX-2026-112</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Personnel</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Postdoc Stipend (Q2) - Dr. A. Novak</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" t="n">
         <v>12500</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>A.1. Staff</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>TRX-2026-113</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Publications</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Page charges - Astrophysical Journal Letters</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" t="n">
         <v>1850</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>B.4. Publications</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>TRX-2026-114</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Server Rack UPS replacement</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" t="n">
         <v>950</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>B.3. Equipment</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>TRX-2026-115</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>AWS S3 Data Egress - Sharing coronal mass ejection dataset</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>890.45</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>B.2. Consumables</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Pending Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TRX-2026-116</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cluster time</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B.2. Consumables</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TRX-2026-117</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AGU conference</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>850</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>B.1. Travel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TRX-2026-118</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>computing item</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>800</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>B.2. Consumables</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
